--- a/RESULTS/tables/table4_external_validation_paper_friendly.xlsx
+++ b/RESULTS/tables/table4_external_validation_paper_friendly.xlsx
@@ -493,37 +493,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.887 (0.878-0.895)</t>
+          <t>0.887 (0.879-0.895)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.828 (0.821-0.835)</t>
+          <t>0.828 (0.821-0.836)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.856 (0.835-0.876)</t>
+          <t>0.856 (0.836-0.878)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.482 (0.460-0.505)</t>
+          <t>0.482 (0.461-0.505)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.482 (0.460-0.505)</t>
+          <t>0.482 (0.461-0.505)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.968 (0.962-0.972)</t>
+          <t>0.968 (0.963-0.973)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.856 (0.835-0.876)</t>
+          <t>0.856 (0.836-0.878)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.617 (0.596-0.636)</t>
+          <t>0.617 (0.596-0.637)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -560,37 +560,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.648 (0.614-0.682)</t>
+          <t>0.648 (0.616-0.682)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.235 (0.215-0.255)</t>
+          <t>0.235 (0.215-0.254)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.235 (0.215-0.255)</t>
+          <t>0.235 (0.215-0.254)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.949 (0.942-0.955)</t>
+          <t>0.949 (0.943-0.955)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.648 (0.614-0.682)</t>
+          <t>0.648 (0.616-0.682)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.755 (0.751-0.760)</t>
+          <t>0.755 (0.750-0.760)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.345 (0.320-0.369)</t>
+          <t>0.345 (0.319-0.367)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -617,27 +617,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.853 (0.833-0.874)</t>
+          <t>0.853 (0.834-0.874)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.495 (0.473-0.518)</t>
+          <t>0.495 (0.473-0.517)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.495 (0.473-0.518)</t>
+          <t>0.495 (0.473-0.517)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.966 (0.960-0.971)</t>
+          <t>0.966 (0.961-0.971)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.853 (0.833-0.874)</t>
+          <t>0.853 (0.834-0.874)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -674,27 +674,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.773 (0.752-0.796)</t>
+          <t>0.773 (0.752-0.797)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.513 (0.490-0.535)</t>
+          <t>0.513 (0.490-0.534)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.513 (0.490-0.535)</t>
+          <t>0.513 (0.490-0.534)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.940 (0.933-0.947)</t>
+          <t>0.940 (0.932-0.947)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.773 (0.752-0.796)</t>
+          <t>0.773 (0.752-0.797)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -726,32 +726,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.745 (0.737-0.751)</t>
+          <t>0.745 (0.738-0.752)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.655 (0.620-0.690)</t>
+          <t>0.655 (0.621-0.690)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.229 (0.210-0.248)</t>
+          <t>0.229 (0.211-0.248)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.229 (0.210-0.248)</t>
+          <t>0.229 (0.211-0.248)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.952 (0.945-0.958)</t>
+          <t>0.952 (0.946-0.957)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.655 (0.620-0.690)</t>
+          <t>0.655 (0.621-0.690)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.339 (0.315-0.362)</t>
+          <t>0.339 (0.316-0.362)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -788,17 +788,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.657 (0.622-0.692)</t>
+          <t>0.657 (0.623-0.692)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.228 (0.208-0.247)</t>
+          <t>0.228 (0.209-0.247)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.228 (0.208-0.247)</t>
+          <t>0.228 (0.209-0.247)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.657 (0.622-0.692)</t>
+          <t>0.657 (0.623-0.692)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.163 (0.160-0.166)</t>
+          <t>0.163 (0.159-0.166)</t>
         </is>
       </c>
     </row>
@@ -845,17 +845,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.656 (0.622-0.691)</t>
+          <t>0.656 (0.623-0.691)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.227 (0.208-0.246)</t>
+          <t>0.227 (0.208-0.245)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.227 (0.208-0.246)</t>
+          <t>0.227 (0.208-0.245)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.656 (0.622-0.691)</t>
+          <t>0.656 (0.623-0.691)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.658 (0.623-0.693)</t>
+          <t>0.658 (0.623-0.692)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.229 (0.209-0.248)</t>
+          <t>0.229 (0.209-0.247)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.229 (0.209-0.248)</t>
+          <t>0.229 (0.209-0.247)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.658 (0.623-0.693)</t>
+          <t>0.658 (0.623-0.692)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">

--- a/RESULTS/tables/table4_external_validation_paper_friendly.xlsx
+++ b/RESULTS/tables/table4_external_validation_paper_friendly.xlsx
@@ -493,52 +493,52 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.887 (0.879-0.895)</t>
+          <t>0.898 (0.889-0.906)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.828 (0.821-0.836)</t>
+          <t>0.848 (0.841-0.856)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.856 (0.836-0.878)</t>
+          <t>0.855 (0.836-0.875)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.482 (0.461-0.505)</t>
+          <t>0.567 (0.545-0.590)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.482 (0.461-0.505)</t>
+          <t>0.567 (0.545-0.590)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.968 (0.963-0.973)</t>
+          <t>0.961 (0.956-0.967)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.856 (0.836-0.878)</t>
+          <t>0.855 (0.836-0.875)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.823 (0.817-0.829)</t>
+          <t>0.847 (0.840-0.854)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.617 (0.596-0.637)</t>
+          <t>0.682 (0.663-0.701)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.122 (0.118-0.125)</t>
+          <t>0.112 (0.108-0.116)</t>
         </is>
       </c>
     </row>
@@ -550,52 +550,52 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.805 (0.794-0.816)</t>
+          <t>0.869 (0.859-0.878)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.744 (0.737-0.751)</t>
+          <t>0.822 (0.813-0.830)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.648 (0.616-0.682)</t>
+          <t>0.772 (0.750-0.794)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.235 (0.215-0.254)</t>
+          <t>0.536 (0.513-0.558)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.235 (0.215-0.254)</t>
+          <t>0.536 (0.513-0.558)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.949 (0.943-0.955)</t>
+          <t>0.937 (0.929-0.944)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.648 (0.616-0.682)</t>
+          <t>0.772 (0.750-0.794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.755 (0.750-0.760)</t>
+          <t>0.834 (0.827-0.841)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.345 (0.319-0.367)</t>
+          <t>0.633 (0.613-0.652)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.162 (0.159-0.166)</t>
+          <t>0.129 (0.124-0.133)</t>
         </is>
       </c>
     </row>
@@ -607,52 +607,52 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.886 (0.878-0.895)</t>
+          <t>0.894 (0.885-0.902)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.831 (0.824-0.838)</t>
+          <t>0.843 (0.835-0.851)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.853 (0.834-0.874)</t>
+          <t>0.857 (0.837-0.876)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.495 (0.473-0.517)</t>
+          <t>0.544 (0.520-0.565)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.495 (0.473-0.517)</t>
+          <t>0.544 (0.520-0.565)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.966 (0.961-0.971)</t>
+          <t>0.963 (0.958-0.969)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.853 (0.834-0.874)</t>
+          <t>0.857 (0.837-0.876)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.827 (0.820-0.833)</t>
+          <t>0.840 (0.833-0.847)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.627 (0.606-0.646)</t>
+          <t>0.665 (0.645-0.684)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.125 (0.121-0.128)</t>
+          <t>0.117 (0.114-0.121)</t>
         </is>
       </c>
     </row>
@@ -664,52 +664,52 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.862 (0.852-0.872)</t>
+          <t>0.878 (0.868-0.887)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.817 (0.809-0.825)</t>
+          <t>0.838 (0.830-0.846)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.773 (0.752-0.797)</t>
+          <t>0.813 (0.793-0.834)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.513 (0.490-0.534)</t>
+          <t>0.563 (0.541-0.586)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.513 (0.490-0.534)</t>
+          <t>0.563 (0.541-0.586)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.940 (0.932-0.947)</t>
+          <t>0.948 (0.941-0.955)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.773 (0.752-0.797)</t>
+          <t>0.813 (0.793-0.834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.828 (0.821-0.834)</t>
+          <t>0.844 (0.837-0.851)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.616 (0.596-0.636)</t>
+          <t>0.666 (0.646-0.684)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.128 (0.124-0.133)</t>
+          <t>0.119 (0.114-0.124)</t>
         </is>
       </c>
     </row>
@@ -721,52 +721,52 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.807 (0.796-0.818)</t>
+          <t>0.869 (0.859-0.878)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.745 (0.738-0.752)</t>
+          <t>0.822 (0.813-0.830)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.655 (0.621-0.690)</t>
+          <t>0.772 (0.750-0.794)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.229 (0.211-0.248)</t>
+          <t>0.536 (0.513-0.558)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.229 (0.211-0.248)</t>
+          <t>0.536 (0.513-0.558)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.952 (0.946-0.957)</t>
+          <t>0.937 (0.929-0.944)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.655 (0.621-0.690)</t>
+          <t>0.772 (0.750-0.794)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.755 (0.750-0.759)</t>
+          <t>0.834 (0.827-0.841)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.339 (0.316-0.362)</t>
+          <t>0.633 (0.613-0.652)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.163 (0.159-0.166)</t>
+          <t>0.129 (0.124-0.133)</t>
         </is>
       </c>
     </row>
@@ -778,52 +778,52 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.806 (0.795-0.817)</t>
+          <t>0.867 (0.857-0.877)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.745 (0.738-0.752)</t>
+          <t>0.821 (0.813-0.829)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.657 (0.623-0.692)</t>
+          <t>0.776 (0.754-0.799)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.228 (0.209-0.247)</t>
+          <t>0.528 (0.505-0.550)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.228 (0.209-0.247)</t>
+          <t>0.528 (0.505-0.550)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.952 (0.946-0.958)</t>
+          <t>0.939 (0.931-0.946)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.657 (0.623-0.692)</t>
+          <t>0.776 (0.754-0.799)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.754 (0.750-0.759)</t>
+          <t>0.832 (0.825-0.839)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.338 (0.314-0.363)</t>
+          <t>0.628 (0.608-0.648)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.163 (0.159-0.166)</t>
+          <t>0.130 (0.125-0.134)</t>
         </is>
       </c>
     </row>
@@ -835,52 +835,52 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.805 (0.795-0.817)</t>
+          <t>0.868 (0.858-0.878)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.745 (0.738-0.751)</t>
+          <t>0.821 (0.813-0.829)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.656 (0.623-0.691)</t>
+          <t>0.774 (0.752-0.796)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.227 (0.208-0.245)</t>
+          <t>0.531 (0.508-0.553)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.227 (0.208-0.245)</t>
+          <t>0.531 (0.508-0.553)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.952 (0.946-0.958)</t>
+          <t>0.938 (0.930-0.945)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.656 (0.623-0.691)</t>
+          <t>0.774 (0.752-0.796)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.754 (0.750-0.759)</t>
+          <t>0.833 (0.826-0.839)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.338 (0.314-0.361)</t>
+          <t>0.630 (0.609-0.649)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.163 (0.160-0.166)</t>
+          <t>0.129 (0.125-0.134)</t>
         </is>
       </c>
     </row>
@@ -892,52 +892,52 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.806 (0.795-0.817)</t>
+          <t>0.868 (0.858-0.877)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.745 (0.738-0.752)</t>
+          <t>0.821 (0.813-0.829)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.658 (0.623-0.692)</t>
+          <t>0.775 (0.753-0.797)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.229 (0.209-0.247)</t>
+          <t>0.529 (0.506-0.552)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.229 (0.209-0.247)</t>
+          <t>0.529 (0.506-0.552)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.952 (0.946-0.958)</t>
+          <t>0.938 (0.931-0.946)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.658 (0.623-0.692)</t>
+          <t>0.775 (0.753-0.797)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.755 (0.750-0.759)</t>
+          <t>0.832 (0.826-0.839)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.339 (0.315-0.363)</t>
+          <t>0.629 (0.609-0.649)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.163 (0.160-0.166)</t>
+          <t>0.129 (0.125-0.134)</t>
         </is>
       </c>
     </row>

--- a/RESULTS/tables/table4_external_validation_paper_friendly.xlsx
+++ b/RESULTS/tables/table4_external_validation_paper_friendly.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>AUROC</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Sensitivity</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Specificity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>PPV</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>NPV</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Brier</t>
         </is>
